--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="217">
   <si>
     <t>##var</t>
   </si>
@@ -627,6 +627,57 @@
   </si>
   <si>
     <t>活动订单</t>
+  </si>
+  <si>
+    <t>棋子自带标签</t>
+  </si>
+  <si>
+    <t>ChessDetailTag</t>
+  </si>
+  <si>
+    <t>SpeedUp</t>
+  </si>
+  <si>
+    <t>加速</t>
+  </si>
+  <si>
+    <t>Delete</t>
+  </si>
+  <si>
+    <t>刪除</t>
+  </si>
+  <si>
+    <t>Sale</t>
+  </si>
+  <si>
+    <t>出售</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>开启</t>
+  </si>
+  <si>
+    <t>Redeem</t>
+  </si>
+  <si>
+    <t>撤回</t>
+  </si>
+  <si>
+    <t>RemoveBubbly</t>
+  </si>
+  <si>
+    <t>删除气泡</t>
+  </si>
+  <si>
+    <t>BuyBubbly</t>
+  </si>
+  <si>
+    <t>购买气泡</t>
+  </si>
+  <si>
+    <t>组合</t>
   </si>
 </sst>
 </file>
@@ -1601,7 +1652,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:L119"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
@@ -2898,7 +2949,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="8:10">
+    <row r="108" ht="12" customHeight="1" spans="8:10">
       <c r="H108" t="s">
         <v>41</v>
       </c>
@@ -2907,6 +2958,117 @@
       </c>
       <c r="J108">
         <v>3</v>
+      </c>
+    </row>
+    <row r="111" customFormat="1" spans="1:10">
+      <c r="A111" t="s">
+        <v>200</v>
+      </c>
+      <c r="B111" t="s">
+        <v>201</v>
+      </c>
+      <c r="C111" t="b">
+        <v>1</v>
+      </c>
+      <c r="D111" t="b">
+        <v>1</v>
+      </c>
+      <c r="H111" t="s">
+        <v>59</v>
+      </c>
+      <c r="I111" t="s">
+        <v>60</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" customFormat="1" spans="8:10">
+      <c r="H112" t="s">
+        <v>202</v>
+      </c>
+      <c r="I112" t="s">
+        <v>203</v>
+      </c>
+      <c r="J112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" customFormat="1" spans="8:10">
+      <c r="H113" t="s">
+        <v>204</v>
+      </c>
+      <c r="I113" t="s">
+        <v>205</v>
+      </c>
+      <c r="J113">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" customFormat="1" spans="8:10">
+      <c r="H114" t="s">
+        <v>206</v>
+      </c>
+      <c r="I114" t="s">
+        <v>207</v>
+      </c>
+      <c r="J114">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" customFormat="1" spans="8:10">
+      <c r="H115" t="s">
+        <v>208</v>
+      </c>
+      <c r="I115" t="s">
+        <v>209</v>
+      </c>
+      <c r="J115">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" customFormat="1" spans="8:10">
+      <c r="H116" t="s">
+        <v>210</v>
+      </c>
+      <c r="I116" t="s">
+        <v>211</v>
+      </c>
+      <c r="J116">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" customFormat="1" spans="8:10">
+      <c r="H117" t="s">
+        <v>212</v>
+      </c>
+      <c r="I117" t="s">
+        <v>213</v>
+      </c>
+      <c r="J117">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="118" customFormat="1" spans="8:10">
+      <c r="H118" t="s">
+        <v>214</v>
+      </c>
+      <c r="I118" t="s">
+        <v>215</v>
+      </c>
+      <c r="J118">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="119" customFormat="1" spans="8:10">
+      <c r="H119" t="s">
+        <v>49</v>
+      </c>
+      <c r="I119" t="s">
+        <v>216</v>
+      </c>
+      <c r="J119">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
